--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -2234,15 +2234,15 @@
   <dimension ref="A1:AP118"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="72.2578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="57.7421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.94140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.94921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.50390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.80859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2253,28 +2253,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.51171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-24</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -629,7 +629,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1031,7 +1031,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1125,7 +1125,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1301,7 +1301,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1330,7 +1330,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1560,7 +1560,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1597,7 +1597,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1672,7 +1672,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1722,7 +1722,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1755,7 +1755,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
